--- a/C84/wykresy.xlsx
+++ b/C84/wykresy.xlsx
@@ -2,22 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bojce\Documents\Projects\Fizyka\C84\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{2AFA23E3-85C2-414E-B381-8FAF6696CD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B218C4-6AB1-48F8-83E4-92140C27B8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-8385" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A" sheetId="1" r:id="rId1"/>
     <sheet name="B" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -264,10 +258,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -276,16 +270,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3553,15 +3547,15 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="15"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="6">
         <v>3</v>
       </c>
       <c r="D19" s="6">
         <v>37</v>
       </c>
-      <c r="E19" s="14"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="5">
         <v>9.2100000000000001E-2</v>
       </c>
@@ -3573,29 +3567,29 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
       <c r="H20" s="9">
         <v>628.20000000000005</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
       <c r="H21" s="9">
         <v>6.5</v>
       </c>
@@ -3829,18 +3823,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="E11:E13"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A14:A16"/>
@@ -3849,10 +3831,23 @@
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="E17:E19"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E5:E7"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3861,349 +3856,350 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="18" defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="18" style="17"/>
+    <col min="1" max="16384" width="18" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17">
+      <c r="A2" s="11">
         <v>10.5</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="11">
         <v>0.2</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="11">
         <v>0.20552000000000001</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="11">
         <v>3.8400000000000001E-3</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="11">
         <v>15</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="11">
         <v>0.2</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="11">
         <v>0.24254000000000001</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="11">
         <v>3.15E-3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17">
+      <c r="A4" s="11">
         <v>19</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="11">
         <v>0.2</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="11">
         <v>0.26195000000000002</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="11">
         <v>2.6700000000000001E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
+      <c r="A5" s="11">
         <v>21</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="11">
         <v>0.2</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="11">
         <v>0.25390000000000001</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="11">
         <v>2.3600000000000001E-3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17">
+      <c r="A6" s="11">
         <v>25</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="11">
         <v>0.2</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="11">
         <v>0.26763999999999999</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="11">
         <v>2.0899999999999998E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17">
+      <c r="A7" s="11">
         <v>29</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="11">
         <v>0.2</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="11">
         <v>0.27851999999999999</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="11">
         <v>1.8799999999999999E-3</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17">
+      <c r="A8" s="11">
         <v>33.5</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="11">
         <v>0.2</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="11">
         <v>0.29132999999999998</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="11">
         <v>1.7099999999999999E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+      <c r="A9" s="11">
         <v>35.5</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="11">
         <v>0.2</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="11">
         <v>0.28367999999999999</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="11">
         <v>1.57E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17">
+      <c r="A10" s="11">
         <v>39</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="11">
         <v>0.2</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="11">
         <v>0.28734999999999999</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="11">
         <v>1.4499999999999999E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17">
+      <c r="A11" s="11">
         <v>43.5</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="11">
         <v>0.2</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="11">
         <v>0.29360999999999998</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="11">
         <v>1.3500000000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17">
+      <c r="A12" s="11">
         <v>46</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="11">
         <v>0.2</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="11">
         <v>0.29319000000000001</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="11">
         <v>1.2600000000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="11">
         <v>0.26901999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="11">
         <v>7.9500000000000005E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="11">
         <v>2.335</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="11">
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
+      <c r="A19" s="11">
         <v>1</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="11">
         <v>0.20552000000000001</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="11">
         <v>3.8400000000000001E-3</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17">
+      <c r="A20" s="11">
         <v>2</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="11">
         <v>0.24254000000000001</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="11">
         <v>3.15E-3</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17">
+      <c r="A21" s="11">
         <v>3</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="11">
         <v>0.26195000000000002</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="11">
         <v>2.6700000000000001E-3</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17">
+      <c r="A22" s="11">
         <v>4</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="11">
         <v>0.25390000000000001</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="11">
         <v>2.3600000000000001E-3</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17">
+      <c r="A23" s="11">
         <v>5</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="11">
         <v>0.26763999999999999</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="11">
         <v>2.0899999999999998E-3</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17">
+      <c r="A24" s="11">
         <v>6</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="11">
         <v>0.27851999999999999</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="11">
         <v>1.8799999999999999E-3</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17">
+      <c r="A25" s="11">
         <v>7</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="11">
         <v>0.29132999999999998</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="11">
         <v>1.7099999999999999E-3</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="17">
+      <c r="A26" s="11">
         <v>8</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="11">
         <v>0.28367999999999999</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="11">
         <v>1.57E-3</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17">
+      <c r="A27" s="11">
         <v>9</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="11">
         <v>0.28734999999999999</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="11">
         <v>1.4499999999999999E-3</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17">
+      <c r="A28" s="11">
         <v>10</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="11">
         <v>0.29360999999999998</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="11">
         <v>1.3500000000000001E-3</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17">
+      <c r="A29" s="11">
         <v>11</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="11">
         <v>0.29319000000000001</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="11">
         <v>1.2600000000000001E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>